--- a/public/downloads/HamkinsCoordination2025.xlsx
+++ b/public/downloads/HamkinsCoordination2025.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
@@ -659,10 +682,10 @@
         <v>84</v>
       </c>
       <c r="N3" s="5">
-        <v>383.1883430480957</v>
+        <v>383188.3430480957</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03520657323117381</v>
+        <v>35.20657323117381</v>
       </c>
       <c r="P3" s="5">
         <v>10884</v>
@@ -709,10 +732,10 @@
         <v>84</v>
       </c>
       <c r="N4" s="5">
-        <v>675.4037458896637</v>
+        <v>675403.7458896637</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05143973692990584</v>
+        <v>51.43973692990584</v>
       </c>
       <c r="P4" s="5">
         <v>13130</v>
@@ -759,10 +782,10 @@
         <v>84</v>
       </c>
       <c r="N5" s="5">
-        <v>1218.132376194</v>
+        <v>1218132.376194</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1452405360908549</v>
+        <v>145.2405360908549</v>
       </c>
       <c r="P5" s="5">
         <v>8387</v>
@@ -809,10 +832,10 @@
         <v>84</v>
       </c>
       <c r="N6" s="5">
-        <v>869.2218019962311</v>
+        <v>869221.8019962311</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08644672322190264</v>
+        <v>86.44672322190264</v>
       </c>
       <c r="P6" s="5">
         <v>10055</v>
@@ -859,10 +882,10 @@
         <v>84</v>
       </c>
       <c r="N7" s="5">
-        <v>1715.888276100159</v>
+        <v>1715888.276100159</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1946775897549533</v>
+        <v>194.6775897549533</v>
       </c>
       <c r="P7" s="5">
         <v>8814</v>
@@ -909,10 +932,10 @@
         <v>84</v>
       </c>
       <c r="N8" s="5">
-        <v>173.3810765743256</v>
+        <v>173381.0765743256</v>
       </c>
       <c r="O8" s="4">
-        <v>0.0148112998952952</v>
+        <v>14.8112998952952</v>
       </c>
       <c r="P8" s="5">
         <v>11706</v>
@@ -959,10 +982,10 @@
         <v>84</v>
       </c>
       <c r="N9" s="5">
-        <v>448.9931247234344</v>
+        <v>448993.1247234344</v>
       </c>
       <c r="O9" s="4">
-        <v>0.0296345538065761</v>
+        <v>29.6345538065761</v>
       </c>
       <c r="P9" s="5">
         <v>15151</v>
@@ -1009,10 +1032,10 @@
         <v>84</v>
       </c>
       <c r="N10" s="5">
-        <v>686.5610625743866</v>
+        <v>686561.0625743866</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08056337274986936</v>
+        <v>80.56337274986936</v>
       </c>
       <c r="P10" s="5">
         <v>8522</v>
@@ -1059,10 +1082,10 @@
         <v>84</v>
       </c>
       <c r="N11" s="5">
-        <v>384.2252945899963</v>
+        <v>384225.2945899963</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04006520277267949</v>
+        <v>40.06520277267949</v>
       </c>
       <c r="P11" s="5">
         <v>9590</v>
@@ -1109,10 +1132,10 @@
         <v>84</v>
       </c>
       <c r="N12" s="5">
-        <v>180.9752416610718</v>
+        <v>180975.2416610718</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01991803232017079</v>
+        <v>19.91803232017079</v>
       </c>
       <c r="P12" s="5">
         <v>9086</v>
@@ -1159,10 +1182,10 @@
         <v>84</v>
       </c>
       <c r="N13" s="5">
-        <v>942.3396553993225</v>
+        <v>942339.6553993225</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07940841454447818</v>
+        <v>79.40841454447818</v>
       </c>
       <c r="P13" s="5">
         <v>11867</v>
@@ -1209,10 +1232,10 @@
         <v>84</v>
       </c>
       <c r="N14" s="5">
-        <v>4900.753338336945</v>
+        <v>4900753.338336945</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2668093063118981</v>
+        <v>266.8093063118981</v>
       </c>
       <c r="P14" s="5">
         <v>18368</v>
@@ -1259,10 +1282,10 @@
         <v>84</v>
       </c>
       <c r="N15" s="5">
-        <v>2100.987360954285</v>
+        <v>2100987.360954285</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2584876182276433</v>
+        <v>258.4876182276433</v>
       </c>
       <c r="P15" s="5">
         <v>8128</v>
@@ -1309,10 +1332,10 @@
         <v>84</v>
       </c>
       <c r="N16" s="5">
-        <v>2251.869577646255</v>
+        <v>2251869.577646255</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09960498839553501</v>
+        <v>99.60498839553502</v>
       </c>
       <c r="P16" s="5">
         <v>22608</v>
@@ -1359,10 +1382,10 @@
         <v>84</v>
       </c>
       <c r="N17" s="5">
-        <v>766.4876019954681</v>
+        <v>766487.6019954681</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09774134174897579</v>
+        <v>97.7413417489758</v>
       </c>
       <c r="P17" s="5">
         <v>7842</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,66 +1497,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2274450118596858</v>
+        <v>0.2357839727887756</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2237760096205224</v>
+        <v>0.2357839727887756</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1802645533063374</v>
+        <v>0.2094992106376795</v>
       </c>
       <c r="E3" s="4">
-        <v>92.04365079365083</v>
+        <v>88.60827664399095</v>
       </c>
       <c r="F3" s="4">
-        <v>92.48135719612196</v>
+        <v>89.74272930648765</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.03704064315817189</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2423516024720329</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2423516024720329</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2531093239685366</v>
+        <v>0.2979786550642818</v>
       </c>
       <c r="C4" s="4">
-        <v>0.243614157873687</v>
+        <v>0.3030590484851802</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1830765953369811</v>
+        <v>0.2818666444376112</v>
       </c>
       <c r="E4" s="4">
-        <v>91.24433106575968</v>
+        <v>88.75850340136056</v>
       </c>
       <c r="F4" s="4">
-        <v>90.21066368381788</v>
+        <v>88.3594332587617</v>
       </c>
       <c r="G4" s="5">
         <v>36</v>
@@ -1528,64 +1601,98 @@
         <v>34</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2278898748518381</v>
+      </c>
+      <c r="O4" s="5">
+        <v>34</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2438634515244659</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2457605976783163</v>
+      </c>
+      <c r="R4" s="5">
+        <v>34</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3779062823772488</v>
+        <v>0.5307512792611598</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4344719062330853</v>
+        <v>0.6427235043022232</v>
       </c>
       <c r="D5" s="4">
-        <v>0.248430848385926</v>
+        <v>0.521559375746928</v>
       </c>
       <c r="E5" s="4">
-        <v>86.02891156462536</v>
+        <v>75.02551020408163</v>
       </c>
       <c r="F5" s="4">
-        <v>82.57084265473337</v>
+        <v>60.18456375838949</v>
       </c>
       <c r="G5" s="5">
         <v>12</v>
       </c>
       <c r="H5" s="5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5">
         <v>8</v>
       </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5307512792611598</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6427235043022232</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1703,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1722,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1764,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,75 +1795,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4062030367338146</v>
+        <v>0.4983265122129418</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4017626288798218</v>
+        <v>0.5248389604087933</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3528085829214223</v>
+        <v>0.4824603812873099</v>
       </c>
       <c r="E3" s="4">
-        <v>90.27683295540439</v>
+        <v>83.79251700680278</v>
       </c>
       <c r="F3" s="4">
-        <v>91.21053939845829</v>
+        <v>84.10017399950198</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5118782657226664</v>
+      </c>
+      <c r="O3" s="5">
+        <v>32</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3049085365268952</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2942100422494502</v>
+      </c>
+      <c r="R3" s="5">
+        <v>32</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.279812796349831</v>
+        <v>0.3718188881179185</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2821405995806563</v>
+        <v>0.3787236002311812</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2332753756854286</v>
+        <v>0.3291373000509697</v>
       </c>
       <c r="E4" s="4">
-        <v>89.38397581254725</v>
+        <v>84.60411942554778</v>
       </c>
       <c r="F4" s="4">
-        <v>88.87459607258238</v>
+        <v>85.17555306984784</v>
       </c>
       <c r="G4" s="5">
         <v>36</v>
       </c>
       <c r="H4" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>1</v>
@@ -1755,25 +1913,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2949671686371668</v>
+      </c>
+      <c r="O4" s="5">
+        <v>33</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2561425649921415</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2549874205442926</v>
+      </c>
+      <c r="R4" s="5">
+        <v>33</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.496671719294838</v>
+        <v>0.5860240506302858</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4708183865057991</v>
+        <v>0.713607907960813</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3104509191398061</v>
+        <v>0.6351360481092266</v>
       </c>
       <c r="E5" s="4">
-        <v>83.47222222222202</v>
+        <v>80.38265306122435</v>
       </c>
       <c r="F5" s="4">
-        <v>79.63273676361075</v>
+        <v>76.45041014168535</v>
       </c>
       <c r="G5" s="5">
         <v>12</v>
@@ -1782,23 +1958,41 @@
         <v>9</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.6587424807077961</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4836490327756151</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4388777862181785</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2003,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2022,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2064,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,107 +2095,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.240862955930449</v>
+        <v>0.2274450118596858</v>
       </c>
       <c r="C3" s="4">
-        <v>0.240862955930449</v>
+        <v>0.2237760096205224</v>
       </c>
       <c r="D3" s="4">
-        <v>0.176003981215008</v>
+        <v>0.1802645533063374</v>
       </c>
       <c r="E3" s="4">
-        <v>92.80328798185943</v>
+        <v>92.04365079365083</v>
       </c>
       <c r="F3" s="4">
-        <v>93.10558041262729</v>
+        <v>92.48135719612196</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.03563761550456829</v>
+      </c>
+      <c r="O3" s="5">
+        <v>35</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2363002950139888</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2339025184507932</v>
+      </c>
+      <c r="R3" s="5">
+        <v>35</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2533793047298166</v>
+        <v>0.2531093239685366</v>
       </c>
       <c r="C4" s="4">
-        <v>0.244986837672153</v>
+        <v>0.243614157873687</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2011646696716277</v>
+        <v>0.1830765953369811</v>
       </c>
       <c r="E4" s="4">
-        <v>91.88586545729405</v>
+        <v>91.24433106575968</v>
       </c>
       <c r="F4" s="4">
-        <v>90.98931145910953</v>
+        <v>90.21066368381788</v>
       </c>
       <c r="G4" s="5">
         <v>36</v>
       </c>
       <c r="H4" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.06993797356461202</v>
+      </c>
+      <c r="O4" s="5">
+        <v>34</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2590528923027943</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2499073478746658</v>
+      </c>
+      <c r="R4" s="5">
+        <v>34</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3802630848006269</v>
+        <v>0.3779062823772488</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3681071404931693</v>
+        <v>0.4344719062330853</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2188139593033895</v>
+        <v>0.248430848385926</v>
       </c>
       <c r="E5" s="4">
-        <v>81.98696145124713</v>
+        <v>86.02891156462536</v>
       </c>
       <c r="F5" s="4">
-        <v>73.56450410141505</v>
+        <v>82.57084265473337</v>
       </c>
       <c r="G5" s="5">
         <v>12</v>
@@ -1995,23 +2258,41 @@
         <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2272393062290163</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4426309876792399</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4747491376288178</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2303,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2322,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2364,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,34 +2395,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.522237627034516</v>
+        <v>0.4062030367338146</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5211911689637055</v>
+        <v>0.4017626288798218</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5118900289449163</v>
+        <v>0.3528085829214223</v>
       </c>
       <c r="E3" s="4">
-        <v>87.01530612244902</v>
+        <v>90.27683295540439</v>
       </c>
       <c r="F3" s="4">
-        <v>83.97464578672486</v>
+        <v>91.21053939845829</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -2140,25 +2454,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3894869430956435</v>
+      </c>
+      <c r="O3" s="5">
+        <v>35</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2660962977290733</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.268781038563392</v>
+      </c>
+      <c r="R3" s="5">
+        <v>35</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2505069049636535</v>
+        <v>0.279812796349831</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2506617924971308</v>
+        <v>0.2821405995806563</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2255788953361046</v>
+        <v>0.2332753756854286</v>
       </c>
       <c r="E4" s="4">
-        <v>85.97411186696901</v>
+        <v>89.38397581254725</v>
       </c>
       <c r="F4" s="4">
-        <v>83.23887646035325</v>
+        <v>88.87459607258238</v>
       </c>
       <c r="G4" s="5">
         <v>36</v>
@@ -2181,34 +2513,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.119112985552626</v>
+      </c>
+      <c r="O4" s="5">
+        <v>34</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2548206221168438</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2613319709695349</v>
+      </c>
+      <c r="R4" s="5">
+        <v>34</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6064525404882772</v>
+        <v>0.496671719294838</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7075884999426236</v>
+        <v>0.4708183865057991</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5668687026807598</v>
+        <v>0.3104509191398061</v>
       </c>
       <c r="E5" s="4">
-        <v>80.71428571428548</v>
+        <v>83.47222222222202</v>
       </c>
       <c r="F5" s="4">
-        <v>74.83314690529495</v>
+        <v>79.63273676361075</v>
       </c>
       <c r="G5" s="5">
         <v>12</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
         <v>1</v>
@@ -2222,9 +2572,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3907373334898428</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4645699784997169</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3846008061689885</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2603,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2611,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2622,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2664,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2695,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6264264100852923</v>
+        <v>0.240862955930449</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4927223444402976</v>
+        <v>0.240862955930449</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5072554678764821</v>
+        <v>0.176003981215008</v>
       </c>
       <c r="E3" s="4">
-        <v>63.19349962207099</v>
+        <v>92.80328798185943</v>
       </c>
       <c r="F3" s="4">
-        <v>72.49968928660087</v>
+        <v>93.10558041262729</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.135093995297591</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.249786223942539</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.249786223942539</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5576806927977694</v>
+        <v>0.2533793047298166</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5289078735504473</v>
+        <v>0.244986837672153</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5910560743933304</v>
+        <v>0.2011646696716277</v>
       </c>
       <c r="E4" s="4">
-        <v>65.10487528344673</v>
+        <v>91.88586545729405</v>
       </c>
       <c r="F4" s="4">
-        <v>75.63851603281104</v>
+        <v>90.98931145910953</v>
       </c>
       <c r="G4" s="5">
         <v>36</v>
       </c>
       <c r="H4" s="5">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.03007335541210198</v>
+      </c>
+      <c r="O4" s="5">
+        <v>35</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2466963368604606</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2389721665897325</v>
+      </c>
+      <c r="R4" s="5">
+        <v>35</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5221543160277912</v>
+        <v>0.3802630848006269</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4024932121489054</v>
+        <v>0.3681071404931693</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4469518559710308</v>
+        <v>0.2188139593033895</v>
       </c>
       <c r="E5" s="4">
-        <v>55.235260770975</v>
+        <v>81.98696145124713</v>
       </c>
       <c r="F5" s="4">
-        <v>60.92188665175243</v>
+        <v>73.56450410141505</v>
       </c>
       <c r="G5" s="5">
         <v>12</v>
       </c>
       <c r="H5" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.05302230101317562</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4015114279044661</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3734685046423403</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2903,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2911,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2922,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2964,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,34 +2995,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3199137649344755</v>
+        <v>0.522237627034516</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3274816547647346</v>
+        <v>0.5211911689637055</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2830469460101541</v>
+        <v>0.5118900289449163</v>
       </c>
       <c r="E3" s="4">
-        <v>96.27834467120182</v>
+        <v>87.01530612244902</v>
       </c>
       <c r="F3" s="4">
-        <v>95.85819040517028</v>
+        <v>83.97464578672486</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -2566,25 +3054,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5174275080510502</v>
+      </c>
+      <c r="O3" s="5">
+        <v>34</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2618947300272547</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2455339838971934</v>
+      </c>
+      <c r="R3" s="5">
+        <v>34</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4226261975013179</v>
+        <v>0.2505069049636535</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4050575771589476</v>
+        <v>0.2506617924971308</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3865714079866542</v>
+        <v>0.2255788953361046</v>
       </c>
       <c r="E4" s="4">
-        <v>95.63397581254718</v>
+        <v>85.97411186696901</v>
       </c>
       <c r="F4" s="4">
-        <v>94.21482724335003</v>
+        <v>83.23887646035325</v>
       </c>
       <c r="G4" s="5">
         <v>36</v>
@@ -2599,58 +3105,94 @@
         <v>1</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1198015775127885</v>
+      </c>
+      <c r="O4" s="5">
+        <v>34</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2515206864535465</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2517352081923117</v>
+      </c>
+      <c r="R4" s="5">
+        <v>34</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6515553056353097</v>
+        <v>0.6064525404882772</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4588934086373188</v>
+        <v>0.7075884999426236</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4567613057939581</v>
+        <v>0.5668687026807598</v>
       </c>
       <c r="E5" s="4">
-        <v>87.96201814058929</v>
+        <v>80.71428571428548</v>
       </c>
       <c r="F5" s="4">
-        <v>80.30574198359331</v>
+        <v>74.83314690529495</v>
       </c>
       <c r="G5" s="5">
         <v>12</v>
       </c>
       <c r="H5" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
         <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.609861483466787</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5171309420060268</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4848891051110904</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3203,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3211,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3222,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3264,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,116 +3295,170 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7749909326905984</v>
+        <v>0.6264264100852923</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7562409618225392</v>
+        <v>0.4927223444402976</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5417635918703471</v>
+        <v>0.5072554678764821</v>
       </c>
       <c r="E3" s="4">
-        <v>48.71693121693141</v>
+        <v>63.19349962207099</v>
       </c>
       <c r="F3" s="4">
-        <v>54.16604523987045</v>
+        <v>72.49968928660087</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4905014272697252</v>
+      </c>
+      <c r="O3" s="5">
+        <v>27</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3983642036222352</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.344429411476682</v>
+      </c>
+      <c r="R3" s="5">
+        <v>27</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4941030962856677</v>
+        <v>0.5576806927977694</v>
       </c>
       <c r="C4" s="4">
-        <v>0.512353490097302</v>
+        <v>0.5289078735504473</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5422210559505944</v>
+        <v>0.5910560743933304</v>
       </c>
       <c r="E4" s="4">
-        <v>60.62547241118679</v>
+        <v>65.10487528344673</v>
       </c>
       <c r="F4" s="4">
-        <v>68.67356450410111</v>
+        <v>75.63851603281104</v>
       </c>
       <c r="G4" s="5">
         <v>36</v>
       </c>
       <c r="H4" s="5">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I4" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.5028749777333656</v>
+      </c>
+      <c r="O4" s="5">
+        <v>29</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2883801832762731</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2441312739581502</v>
+      </c>
+      <c r="R4" s="5">
+        <v>29</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4770269117949761</v>
+        <v>0.5221543160277912</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3554474473438404</v>
+        <v>0.4024932121489054</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4340865062871007</v>
+        <v>0.4469518559710308</v>
       </c>
       <c r="E5" s="4">
-        <v>55.90986394557821</v>
+        <v>55.235260770975</v>
       </c>
       <c r="F5" s="4">
-        <v>59.4546979865771</v>
+        <v>60.92188665175243</v>
       </c>
       <c r="G5" s="5">
         <v>12</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>4</v>
@@ -2861,9 +3472,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.191926478107957</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4853605681813294</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.366836284141822</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3503,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3522,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3564,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,81 +3595,117 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2767403548290738</v>
+        <v>0.3199137649344755</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2767403548290738</v>
+        <v>0.3274816547647346</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2405120277539076</v>
+        <v>0.2830469460101541</v>
       </c>
       <c r="E3" s="4">
-        <v>94.35090702947849</v>
+        <v>96.27834467120182</v>
       </c>
       <c r="F3" s="4">
-        <v>94.48576932637327</v>
+        <v>95.85819040517028</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1871549247463589</v>
+      </c>
+      <c r="O3" s="5">
+        <v>35</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2461007673735074</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2493574377592948</v>
+      </c>
+      <c r="R3" s="5">
+        <v>35</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3228118875996253</v>
+        <v>0.4226261975013179</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3228118875996253</v>
+        <v>0.4050575771589476</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2696977385644518</v>
+        <v>0.3865714079866542</v>
       </c>
       <c r="E4" s="4">
-        <v>93.50151171579746</v>
+        <v>95.63397581254718</v>
       </c>
       <c r="F4" s="4">
-        <v>91.63808103405367</v>
+        <v>94.21482724335003</v>
       </c>
       <c r="G4" s="5">
         <v>36</v>
       </c>
       <c r="H4" s="5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
@@ -3033,40 +3713,58 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.334167730184623</v>
+      </c>
+      <c r="O4" s="5">
+        <v>34</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2320769068225504</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2218042166314037</v>
+      </c>
+      <c r="R4" s="5">
+        <v>34</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4888332021366057</v>
+        <v>0.6515553056353097</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4566033611223372</v>
+        <v>0.4588934086373188</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2907517703682713</v>
+        <v>0.4567613057939581</v>
       </c>
       <c r="E5" s="4">
-        <v>87.72675736961445</v>
+        <v>87.96201814058929</v>
       </c>
       <c r="F5" s="4">
-        <v>82.12061894109044</v>
+        <v>80.30574198359331</v>
       </c>
       <c r="G5" s="5">
         <v>12</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
         <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -3074,9 +3772,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3798418366410853</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3983274145412529</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2961040500768538</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3803,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7749909326905984</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.7562409618225392</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5417635918703471</v>
+      </c>
+      <c r="E3" s="4">
+        <v>48.71693121693141</v>
+      </c>
+      <c r="F3" s="4">
+        <v>54.16604523987045</v>
+      </c>
+      <c r="G3" s="5">
+        <v>36</v>
+      </c>
+      <c r="H3" s="5">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>29</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>29</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.7562409618225392</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3764739763539141</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.288202117857864</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4941030962856677</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.512353490097302</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5422210559505944</v>
+      </c>
+      <c r="E4" s="4">
+        <v>60.62547241118679</v>
+      </c>
+      <c r="F4" s="4">
+        <v>68.67356450410111</v>
+      </c>
+      <c r="G4" s="5">
+        <v>36</v>
+      </c>
+      <c r="H4" s="5">
+        <v>17</v>
+      </c>
+      <c r="I4" s="5">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5">
+        <v>13</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>13</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.4714998864590611</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2746795215950257</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2749762727783488</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4770269117949761</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3554474473438404</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4340865062871007</v>
+      </c>
+      <c r="E5" s="4">
+        <v>55.90986394557821</v>
+      </c>
+      <c r="F5" s="4">
+        <v>59.4546979865771</v>
+      </c>
+      <c r="G5" s="5">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>4</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2849917877588496</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4307787772047187</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2760301687724859</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2767403548290738</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2767403548290738</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2405120277539076</v>
+      </c>
+      <c r="E3" s="4">
+        <v>94.35090702947849</v>
+      </c>
+      <c r="F3" s="4">
+        <v>94.48576932637327</v>
+      </c>
+      <c r="G3" s="5">
+        <v>36</v>
+      </c>
+      <c r="H3" s="5">
+        <v>36</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.06694513225095654</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2611672012322098</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2611672012322098</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3228118875996253</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3228118875996253</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2696977385644518</v>
+      </c>
+      <c r="E4" s="4">
+        <v>93.50151171579746</v>
+      </c>
+      <c r="F4" s="4">
+        <v>91.63808103405367</v>
+      </c>
+      <c r="G4" s="5">
+        <v>36</v>
+      </c>
+      <c r="H4" s="5">
+        <v>36</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.193881335775289</v>
+      </c>
+      <c r="O4" s="5">
+        <v>36</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2570963937779102</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2570963937779102</v>
+      </c>
+      <c r="R4" s="5">
+        <v>36</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4888332021366057</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4566033611223372</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2907517703682713</v>
+      </c>
+      <c r="E5" s="4">
+        <v>87.72675736961445</v>
+      </c>
+      <c r="F5" s="4">
+        <v>82.12061894109044</v>
+      </c>
+      <c r="G5" s="5">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5">
+        <v>9</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.07505821449028754</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.451304094891462</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4315839562922413</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>88.09523809523809</v>
+      </c>
+      <c r="C3" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.3113170753544542</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2793472535725329</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.2320714970607585</v>
+      </c>
+      <c r="K3" s="4">
+        <v>87.36313573048264</v>
+      </c>
+      <c r="L3" s="4">
+        <v>84.58679556834144</v>
+      </c>
+      <c r="M3" s="5">
+        <v>84</v>
+      </c>
+      <c r="N3" s="5">
+        <v>383188.3430480957</v>
+      </c>
+      <c r="O3" s="4">
+        <v>35.20657323117381</v>
+      </c>
+      <c r="P3" s="5">
+        <v>10884</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>80.95238095238095</v>
+      </c>
+      <c r="C4" s="3">
+        <v>13.0952380952381</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5.952380952380952</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="F4" s="3">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.319770412231685</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2557896456820658</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2356914310042401</v>
+      </c>
+      <c r="K4" s="4">
+        <v>87.13232912212553</v>
+      </c>
+      <c r="L4" s="4">
+        <v>84.79586129753875</v>
+      </c>
+      <c r="M4" s="5">
+        <v>84</v>
+      </c>
+      <c r="N4" s="5">
+        <v>675403.7458896637</v>
+      </c>
+      <c r="O4" s="4">
+        <v>51.43973692990584</v>
+      </c>
+      <c r="P4" s="5">
+        <v>13130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>97.61904761904762</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.380952380952381</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2692503303118843</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2612581298294728</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2165551988869899</v>
+      </c>
+      <c r="K5" s="4">
+        <v>90.51425332037572</v>
+      </c>
+      <c r="L5" s="4">
+        <v>90.29588793011671</v>
+      </c>
+      <c r="M5" s="5">
+        <v>84</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1218132.376194</v>
+      </c>
+      <c r="O5" s="4">
+        <v>145.2405360908549</v>
+      </c>
+      <c r="P5" s="5">
+        <v>8387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>88.09523809523809</v>
+      </c>
+      <c r="C6" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.286864872514177</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2673488893431559</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2009094085029245</v>
+      </c>
+      <c r="K6" s="4">
+        <v>88.09766763848403</v>
+      </c>
+      <c r="L6" s="4">
+        <v>86.37490678598239</v>
+      </c>
+      <c r="M6" s="5">
+        <v>84</v>
+      </c>
+      <c r="N6" s="5">
+        <v>869221.8019962311</v>
+      </c>
+      <c r="O6" s="4">
+        <v>86.44672322190264</v>
+      </c>
+      <c r="P6" s="5">
+        <v>10055</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>92.85714285714286</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.292681683305643</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2599105008669966</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.2098051946543648</v>
+      </c>
+      <c r="K7" s="4">
+        <v>91.66950113378688</v>
+      </c>
+      <c r="L7" s="4">
+        <v>90.13968786620065</v>
+      </c>
+      <c r="M7" s="5">
+        <v>84</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1715888.276100159</v>
+      </c>
+      <c r="O7" s="4">
+        <v>194.6775897549533</v>
+      </c>
+      <c r="P7" s="5">
+        <v>8814</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>88.09523809523809</v>
+      </c>
+      <c r="C8" s="3">
+        <v>11.9047619047619</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.2841994916072366</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2655596219900653</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2558953006614135</v>
+      </c>
+      <c r="K8" s="4">
+        <v>86.73226433430517</v>
+      </c>
+      <c r="L8" s="4">
+        <v>84.92729306487487</v>
+      </c>
+      <c r="M8" s="5">
+        <v>84</v>
+      </c>
+      <c r="N8" s="5">
+        <v>173381.0765743256</v>
+      </c>
+      <c r="O8" s="4">
+        <v>14.8112998952952</v>
+      </c>
+      <c r="P8" s="5">
+        <v>11706</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>88.09523809523809</v>
+      </c>
+      <c r="C9" s="3">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.3095431910475323</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.2943135987284821</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.2496356984868976</v>
+      </c>
+      <c r="K9" s="4">
+        <v>83.65322319403941</v>
+      </c>
+      <c r="L9" s="4">
+        <v>83.46822733567639</v>
+      </c>
+      <c r="M9" s="5">
+        <v>84</v>
+      </c>
+      <c r="N9" s="5">
+        <v>448993.1247234344</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.6345538065761</v>
+      </c>
+      <c r="P9" s="5">
+        <v>15151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>91.66666666666666</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.2755272213756556</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2659926113577524</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.205469041264279</v>
+      </c>
+      <c r="K10" s="4">
+        <v>90.8418367346938</v>
+      </c>
+      <c r="L10" s="4">
+        <v>90.09241504207864</v>
+      </c>
+      <c r="M10" s="5">
+        <v>84</v>
+      </c>
+      <c r="N10" s="5">
+        <v>686561.0625743866</v>
+      </c>
+      <c r="O10" s="4">
+        <v>80.56337274986936</v>
+      </c>
+      <c r="P10" s="5">
+        <v>8522</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>92.85714285714286</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2896172482910669</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2788978284385102</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2264131672473226</v>
+      </c>
+      <c r="K11" s="4">
+        <v>88.92209264658257</v>
+      </c>
+      <c r="L11" s="4">
+        <v>88.55544902524849</v>
+      </c>
+      <c r="M11" s="5">
+        <v>84</v>
+      </c>
+      <c r="N11" s="5">
+        <v>384225.2945899963</v>
+      </c>
+      <c r="O11" s="4">
+        <v>40.06520277267949</v>
+      </c>
+      <c r="P11" s="5">
+        <v>9590</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>94.04761904761905</v>
+      </c>
+      <c r="C12" s="3">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2701370157590664</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2575199737938072</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2012266151481129</v>
+      </c>
+      <c r="K12" s="4">
+        <v>90.8649173955297</v>
+      </c>
+      <c r="L12" s="4">
+        <v>89.40702567380175</v>
+      </c>
+      <c r="M12" s="5">
+        <v>84</v>
+      </c>
+      <c r="N12" s="5">
+        <v>180975.2416610718</v>
+      </c>
+      <c r="O12" s="4">
+        <v>19.91803232017079</v>
+      </c>
+      <c r="P12" s="5">
+        <v>9086</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>90.47619047619048</v>
+      </c>
+      <c r="C13" s="3">
+        <v>5.952380952380952</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2939110273497758</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.273503491735946</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2288899359663185</v>
+      </c>
+      <c r="K13" s="4">
+        <v>85.66893424036306</v>
+      </c>
+      <c r="L13" s="4">
+        <v>82.35338766379242</v>
+      </c>
+      <c r="M13" s="5">
+        <v>84</v>
+      </c>
+      <c r="N13" s="5">
+        <v>942339.6553993225</v>
+      </c>
+      <c r="O13" s="4">
+        <v>79.40841454447818</v>
+      </c>
+      <c r="P13" s="5">
+        <v>11867</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>75</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="D14" s="3">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.3636562469824078</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.300750080057929</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.3460935919138404</v>
+      </c>
+      <c r="K14" s="4">
+        <v>62.87576935536109</v>
+      </c>
+      <c r="L14" s="4">
+        <v>72.19092894428515</v>
+      </c>
+      <c r="M14" s="5">
+        <v>84</v>
+      </c>
+      <c r="N14" s="5">
+        <v>4900753.338336945</v>
+      </c>
+      <c r="O14" s="4">
+        <v>266.8093063118981</v>
+      </c>
+      <c r="P14" s="5">
+        <v>18368</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>90.47619047619048</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="D15" s="3">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2618372053042038</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.241336605757645</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2017764067108546</v>
+      </c>
+      <c r="K15" s="4">
+        <v>94.81413994169158</v>
+      </c>
+      <c r="L15" s="4">
+        <v>92.93211356130655</v>
+      </c>
+      <c r="M15" s="5">
+        <v>84</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2100987.360954285</v>
+      </c>
+      <c r="O15" s="4">
+        <v>258.4876182276433</v>
+      </c>
+      <c r="P15" s="5">
+        <v>8128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>34.52380952380953</v>
+      </c>
+      <c r="C16" s="3">
+        <v>10.71428571428571</v>
+      </c>
+      <c r="D16" s="3">
+        <v>54.76190476190477</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>54.76190476190477</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.3406056101502197</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2783504243482554</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.4138648101898807</v>
+      </c>
+      <c r="K16" s="4">
+        <v>54.84815354713315</v>
+      </c>
+      <c r="L16" s="4">
+        <v>61.13907531692767</v>
+      </c>
+      <c r="M16" s="5">
+        <v>84</v>
+      </c>
+      <c r="N16" s="5">
+        <v>2251869.577646255</v>
+      </c>
+      <c r="O16" s="4">
+        <v>99.60498839553502</v>
+      </c>
+      <c r="P16" s="5">
+        <v>22608</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>96.42857142857143</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2865849828459746</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2782931484814135</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2116079862840902</v>
+      </c>
+      <c r="K17" s="4">
+        <v>93.0405733722059</v>
+      </c>
+      <c r="L17" s="4">
+        <v>91.49888143176869</v>
+      </c>
+      <c r="M17" s="5">
+        <v>84</v>
+      </c>
+      <c r="N17" s="5">
+        <v>766487.6019954681</v>
+      </c>
+      <c r="O17" s="4">
+        <v>97.7413417489758</v>
+      </c>
+      <c r="P17" s="5">
+        <v>7842</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3250,10 +5424,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
@@ -3743,7 +5917,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -3847,9 +6021,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>74</v>
+      </c>
+      <c r="C3" s="5">
+        <v>7</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>68</v>
+      </c>
+      <c r="C4" s="5">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>82</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>74</v>
+      </c>
+      <c r="C6" s="5">
+        <v>7</v>
+      </c>
+      <c r="D6" s="5">
+        <v>3</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>78</v>
+      </c>
+      <c r="C7" s="5">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>74</v>
+      </c>
+      <c r="C8" s="5">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>74</v>
+      </c>
+      <c r="C9" s="5">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>77</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>78</v>
+      </c>
+      <c r="C11" s="5">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>79</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>76</v>
+      </c>
+      <c r="C13" s="5">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5">
+        <v>3</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>63</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5">
+        <v>18</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>18</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>7</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>76</v>
+      </c>
+      <c r="C15" s="5">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5">
+        <v>3</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>3</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>2</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>1</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>29</v>
+      </c>
+      <c r="C16" s="5">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>46</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>30</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>81</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6789,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6831,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6862,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3373016642838588</v>
@@ -3960,10 +6921,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2810027420354251</v>
+      </c>
+      <c r="O3" s="5">
+        <v>34</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.268668297358239</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2794979148540224</v>
+      </c>
+      <c r="R3" s="5">
+        <v>34</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2496255777944619</v>
@@ -4001,10 +6980,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.0002015337094225261</v>
+      </c>
+      <c r="O4" s="5">
+        <v>34</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2496031851600816</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2454400811621448</v>
+      </c>
+      <c r="R4" s="5">
+        <v>34</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5634596054748519</v>
@@ -4042,9 +7039,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.6050201253568398</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6244050799262166</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4706341499696249</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7070,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7089,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7131,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7162,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4988454351849462</v>
@@ -4173,10 +7221,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4826177789933662</v>
+      </c>
+      <c r="O3" s="5">
+        <v>28</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3147195220832755</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.240077318255421</v>
+      </c>
+      <c r="R3" s="5">
+        <v>28</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2602609252268853</v>
@@ -4214,17 +7280,33 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1067549110981166</v>
+      </c>
+      <c r="O4" s="5">
+        <v>35</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2502892834782357</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2438746272060862</v>
+      </c>
+      <c r="R4" s="5">
+        <v>35</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>2.914442926181223</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>3.218045065336293</v>
       </c>
@@ -4255,9 +7337,27 @@
       <c r="M5" s="5">
         <v>5</v>
       </c>
+      <c r="N5" s="4">
+        <v>2.991832589187487</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5433664689372609</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4271838086031335</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7368,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7387,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7429,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7460,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.283600387011277</v>
@@ -4386,10 +7519,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2510752142200603</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2297829220943131</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2297829220943131</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.24648146691745</v>
@@ -4427,10 +7578,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1164593481131192</v>
+      </c>
+      <c r="O4" s="5">
+        <v>35</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2538637527843654</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2478930289023583</v>
+      </c>
+      <c r="R4" s="5">
+        <v>35</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3971363081105276</v>
@@ -4468,9 +7637,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1100279383098811</v>
+      </c>
+      <c r="O5" s="5">
+        <v>11</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4338122875471546</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4067932217308141</v>
+      </c>
+      <c r="R5" s="5">
+        <v>11</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7668,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7687,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7729,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7760,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.296320023897709</v>
@@ -4599,10 +7819,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2274954013693949</v>
+      </c>
+      <c r="O3" s="5">
+        <v>35</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2597948596820749</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2567604570696426</v>
+      </c>
+      <c r="R3" s="5">
+        <v>35</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.243681953882645</v>
@@ -4640,10 +7878,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.01703144076074728</v>
+      </c>
+      <c r="O4" s="5">
+        <v>31</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2375543408609851</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2368253296582329</v>
+      </c>
+      <c r="R4" s="5">
+        <v>31</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.4837650256015043</v>
@@ -4681,9 +7937,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3040431641461083</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.516006505970059</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4319520743188541</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7968,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7987,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8029,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8060,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2383386226246474</v>
@@ -4812,10 +8119,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1014466699937715</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2492023595185306</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2492023595185306</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2331439149661594</v>
@@ -4853,10 +8178,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.04114606045504258</v>
+      </c>
+      <c r="O4" s="5">
+        <v>34</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2430071492417269</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2259487166761718</v>
+      </c>
+      <c r="R4" s="5">
+        <v>34</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.4487756442165202</v>
@@ -4894,9 +8237,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2872938801501377</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5721432568587291</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4524347197460994</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8268,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2357839727887756</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2357839727887756</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2094992106376795</v>
-      </c>
-      <c r="E3" s="4">
-        <v>88.60827664399095</v>
-      </c>
-      <c r="F3" s="4">
-        <v>89.74272930648765</v>
-      </c>
-      <c r="G3" s="5">
-        <v>36</v>
-      </c>
-      <c r="H3" s="5">
-        <v>36</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2979786550642818</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3030590484851802</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2818666444376112</v>
-      </c>
-      <c r="E4" s="4">
-        <v>88.75850340136056</v>
-      </c>
-      <c r="F4" s="4">
-        <v>88.3594332587617</v>
-      </c>
-      <c r="G4" s="5">
-        <v>36</v>
-      </c>
-      <c r="H4" s="5">
-        <v>34</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.5307512792611598</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6427235043022232</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.521559375746928</v>
-      </c>
-      <c r="E5" s="4">
-        <v>75.02551020408163</v>
-      </c>
-      <c r="F5" s="4">
-        <v>60.18456375838949</v>
-      </c>
-      <c r="G5" s="5">
-        <v>12</v>
-      </c>
-      <c r="H5" s="5">
-        <v>4</v>
-      </c>
-      <c r="I5" s="5">
-        <v>8</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4983265122129418</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.5248389604087933</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4824603812873099</v>
-      </c>
-      <c r="E3" s="4">
-        <v>83.79251700680278</v>
-      </c>
-      <c r="F3" s="4">
-        <v>84.10017399950198</v>
-      </c>
-      <c r="G3" s="5">
-        <v>36</v>
-      </c>
-      <c r="H3" s="5">
-        <v>32</v>
-      </c>
-      <c r="I3" s="5">
-        <v>4</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3718188881179185</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3787236002311812</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3291373000509697</v>
-      </c>
-      <c r="E4" s="4">
-        <v>84.60411942554778</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.17555306984784</v>
-      </c>
-      <c r="G4" s="5">
-        <v>36</v>
-      </c>
-      <c r="H4" s="5">
-        <v>33</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.5860240506302858</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.713607907960813</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6351360481092266</v>
-      </c>
-      <c r="E5" s="4">
-        <v>80.38265306122435</v>
-      </c>
-      <c r="F5" s="4">
-        <v>76.45041014168535</v>
-      </c>
-      <c r="G5" s="5">
-        <v>12</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>3</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/HamkinsCoordination2025.xlsx
+++ b/public/downloads/HamkinsCoordination2025.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.03704064315817189</v>
+        <v>-0.0343399967741469</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2423516024720329</v>
+        <v>0.2336582019549193</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2423516024720329</v>
+        <v>0.2336582019549193</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2278898748518381</v>
+        <v>0.1754557541051156</v>
       </c>
       <c r="O4" s="5">
         <v>34</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2438634515244659</v>
+        <v>0.2400864716579808</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2457605976783163</v>
+        <v>0.2417614425255674</v>
       </c>
       <c r="R4" s="5">
         <v>34</v>
@@ -1855,16 +1855,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5118782657226664</v>
+        <v>0.4384783776281864</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3049085365268952</v>
+        <v>0.2915027727615009</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2942100422494502</v>
+        <v>0.2837160510192867</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -1914,16 +1914,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2949671686371668</v>
+        <v>0.274797480553616</v>
       </c>
       <c r="O4" s="5">
         <v>33</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2561425649921415</v>
+        <v>0.2542570646994378</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2549874205442926</v>
+        <v>0.2535417138032688</v>
       </c>
       <c r="R4" s="5">
         <v>33</v>
@@ -1973,16 +1973,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6587424807077961</v>
+        <v>0.558219116970804</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4836490327756151</v>
+        <v>0.4501412448632844</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4388777862181785</v>
+        <v>0.427708523580735</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -2155,16 +2155,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.03563761550456829</v>
+        <v>-0.06381177032996632</v>
       </c>
       <c r="O3" s="5">
         <v>35</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2363002950139888</v>
+        <v>0.2192082507459887</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2339025184507932</v>
+        <v>0.2134807190370064</v>
       </c>
       <c r="R3" s="5">
         <v>35</v>
@@ -2214,16 +2214,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06993797356461202</v>
+        <v>0.01691808310084753</v>
       </c>
       <c r="O4" s="5">
         <v>34</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2590528923027943</v>
+        <v>0.2519627640856215</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2499073478746658</v>
+        <v>0.2424001532917769</v>
       </c>
       <c r="R4" s="5">
         <v>34</v>
@@ -2273,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2272393062290163</v>
+        <v>0.03306519032304323</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4426309876792399</v>
+        <v>0.3802565850415885</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4747491376288178</v>
+        <v>0.429731062648834</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -2455,16 +2455,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3894869430956435</v>
+        <v>0.3141624348266703</v>
       </c>
       <c r="O3" s="5">
         <v>35</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2660962977290733</v>
+        <v>0.2592012741720922</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.268781038563392</v>
+        <v>0.2595368855256692</v>
       </c>
       <c r="R3" s="5">
         <v>35</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.119112985552626</v>
+        <v>0.09823388492188201</v>
       </c>
       <c r="O4" s="5">
         <v>34</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2548206221168438</v>
+        <v>0.253034057508683</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2613319709695349</v>
+        <v>0.2594403143256</v>
       </c>
       <c r="R4" s="5">
         <v>34</v>
@@ -2573,16 +2573,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3907373334898428</v>
+        <v>0.2633926322094453</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4645699784997169</v>
+        <v>0.4401022453580765</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3846008061689885</v>
+        <v>0.3661265732335121</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -2755,16 +2755,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.135093995297591</v>
+        <v>0.04605336829347095</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.249786223942539</v>
+        <v>0.2363768560991741</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.249786223942539</v>
+        <v>0.2363768560991741</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -2814,16 +2814,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03007335541210198</v>
+        <v>-0.1202062909277117</v>
       </c>
       <c r="O4" s="5">
         <v>35</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2466963368604606</v>
+        <v>0.2331397200292989</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2389721665897325</v>
+        <v>0.2276034445781266</v>
       </c>
       <c r="R4" s="5">
         <v>35</v>
@@ -2873,16 +2873,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.05302230101317562</v>
+        <v>-0.02529039103272623</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4015114279044661</v>
+        <v>0.3718329544563848</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3734685046423403</v>
+        <v>0.3681071404931693</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -3055,16 +3055,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5174275080510502</v>
+        <v>0.4370542951880054</v>
       </c>
       <c r="O3" s="5">
         <v>34</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2618947300272547</v>
+        <v>0.2488145141699213</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2455339838971934</v>
+        <v>0.231684343577664</v>
       </c>
       <c r="R3" s="5">
         <v>34</v>
@@ -3114,16 +3114,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1198015775127885</v>
+        <v>0.04970661760009421</v>
       </c>
       <c r="O4" s="5">
         <v>34</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2515206864535465</v>
+        <v>0.2444732685785603</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2517352081923117</v>
+        <v>0.2442732363246792</v>
       </c>
       <c r="R4" s="5">
         <v>34</v>
@@ -3173,16 +3173,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.609861483466787</v>
+        <v>0.4023887650732263</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5171309420060268</v>
+        <v>0.4302160133951863</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4848891051110904</v>
+        <v>0.4378786366064489</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -3355,16 +3355,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4905014272697252</v>
+        <v>-0.4847271425359452</v>
       </c>
       <c r="O3" s="5">
         <v>27</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3983642036222352</v>
+        <v>0.3986849972185563</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.344429411476682</v>
+        <v>0.3442155490791347</v>
       </c>
       <c r="R3" s="5">
         <v>27</v>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5028749777333656</v>
+        <v>-0.5407657873235223</v>
       </c>
       <c r="O4" s="5">
         <v>29</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2883801832762731</v>
+        <v>0.2854736563052079</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2441312739581502</v>
+        <v>0.2403516496949132</v>
       </c>
       <c r="R4" s="5">
         <v>29</v>
@@ -3473,16 +3473,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.191926478107957</v>
+        <v>-0.4249412840977698</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4853605681813294</v>
+        <v>0.4465247671830273</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.366836284141822</v>
+        <v>0.3335484547147059</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -3655,16 +3655,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1871549247463589</v>
+        <v>-0.2638731963613736</v>
       </c>
       <c r="O3" s="5">
         <v>35</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2461007673735074</v>
+        <v>0.2303163547670337</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2493574377592948</v>
+        <v>0.2309300913179214</v>
       </c>
       <c r="R3" s="5">
         <v>35</v>
@@ -3714,16 +3714,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.334167730184623</v>
+        <v>-0.411593915275887</v>
       </c>
       <c r="O4" s="5">
         <v>34</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2320769068225504</v>
+        <v>0.2168520147238462</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2218042166314037</v>
+        <v>0.2056837426445405</v>
       </c>
       <c r="R4" s="5">
         <v>34</v>
@@ -3773,16 +3773,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3798418366410853</v>
+        <v>-0.5250255313834771</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3983274145412529</v>
+        <v>0.312929153844913</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2961040500768538</v>
+        <v>0.2342215282321181</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -3955,16 +3955,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7562409618225392</v>
+        <v>-0.6230148155489124</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3764739763539141</v>
+        <v>0.3909959873013735</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.288202117857864</v>
+        <v>0.2691698112473459</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -4014,16 +4014,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4714998864590611</v>
+        <v>-0.5159773296775256</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2746795215950257</v>
+        <v>0.2801922188004021</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2749762727783488</v>
+        <v>0.2718564859218939</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -4073,16 +4073,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2849917877588496</v>
+        <v>-0.4074324319728362</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4307787772047187</v>
+        <v>0.4307787772047186</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2760301687724859</v>
+        <v>0.2515420399296886</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -4255,16 +4255,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.06694513225095654</v>
+        <v>-0.1614143455583203</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2611672012322098</v>
+        <v>0.248368750279217</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2611672012322098</v>
+        <v>0.248368750279217</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -4314,16 +4314,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.193881335775289</v>
+        <v>-0.2739398248004363</v>
       </c>
       <c r="O4" s="5">
         <v>36</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2570963937779102</v>
+        <v>0.2442843784742443</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2570963937779102</v>
+        <v>0.2442843784742443</v>
       </c>
       <c r="R4" s="5">
         <v>36</v>
@@ -4373,16 +4373,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.07505821449028754</v>
+        <v>-0.2424256480113627</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.451304094891462</v>
+        <v>0.3951707661224599</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4315839562922413</v>
+        <v>0.412528662440597</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -4519,13 +4519,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.3113170753544542</v>
+        <v>0.2957944129515446</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2793472535725329</v>
+        <v>0.268462880125106</v>
       </c>
       <c r="J3" s="4">
-        <v>0.2320714970607585</v>
+        <v>0.228347860346899</v>
       </c>
       <c r="K3" s="4">
         <v>87.36313573048264</v>
@@ -4569,13 +4569,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.319770412231685</v>
+        <v>0.30925862447584</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2557896456820658</v>
+        <v>0.2461659306536691</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2356914310042401</v>
+        <v>0.2356187042473508</v>
       </c>
       <c r="K4" s="4">
         <v>87.13232912212553</v>
@@ -4619,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2692503303118843</v>
+        <v>0.2488017609532312</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2612581298294728</v>
+        <v>0.2432117757732307</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2165551988869899</v>
+        <v>0.2038040244889655</v>
       </c>
       <c r="K5" s="4">
         <v>90.51425332037572</v>
@@ -4669,13 +4669,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.286864872514177</v>
+        <v>0.2728371042852495</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2673488893431559</v>
+        <v>0.2526403400153082</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2009094085029245</v>
+        <v>0.2007650845517231</v>
       </c>
       <c r="K6" s="4">
         <v>88.09766763848403</v>
@@ -4719,13 +4719,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.292681683305643</v>
+        <v>0.2651906149469874</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2599105008669966</v>
+        <v>0.2435280261092753</v>
       </c>
       <c r="J7" s="4">
-        <v>0.2098051946543648</v>
+        <v>0.1810999491159779</v>
       </c>
       <c r="K7" s="4">
         <v>91.66950113378688</v>
@@ -4769,13 +4769,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.2841994916072366</v>
+        <v>0.2788550428714086</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2655596219900653</v>
+        <v>0.2594929504520984</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2558953006614135</v>
+        <v>0.2519199626876917</v>
       </c>
       <c r="K8" s="4">
         <v>86.73226433430517</v>
@@ -4819,13 +4819,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.3095431910475323</v>
+        <v>0.2982029653208715</v>
       </c>
       <c r="I9" s="4">
-        <v>0.2943135987284821</v>
+        <v>0.2877725256804278</v>
       </c>
       <c r="J9" s="4">
-        <v>0.2496356984868976</v>
+        <v>0.2392054761529851</v>
       </c>
       <c r="K9" s="4">
         <v>83.65322319403941</v>
@@ -4869,13 +4869,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2755272213756556</v>
+        <v>0.2562528042194885</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2659926113577524</v>
+        <v>0.2487179075247573</v>
       </c>
       <c r="J10" s="4">
-        <v>0.205469041264279</v>
+        <v>0.1833729638162331</v>
       </c>
       <c r="K10" s="4">
         <v>90.8418367346938</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.2896172482910669</v>
+        <v>0.2824011772000574</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2788978284385102</v>
+        <v>0.2717936005073132</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2264131672473226</v>
+        <v>0.2128479482505297</v>
       </c>
       <c r="K11" s="4">
         <v>88.92209264658257</v>
@@ -4969,13 +4969,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2701370157590664</v>
+        <v>0.2543403832631149</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2575199737938072</v>
+        <v>0.2458296772626589</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2012266151481129</v>
+        <v>0.186274484391626</v>
       </c>
       <c r="K12" s="4">
         <v>90.8649173955297</v>
@@ -5019,13 +5019,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.2939110273497758</v>
+        <v>0.2728684802343759</v>
       </c>
       <c r="I13" s="4">
-        <v>0.273503491735946</v>
+        <v>0.2590208790727797</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2288899359663185</v>
+        <v>0.223358951426247</v>
       </c>
       <c r="K13" s="4">
         <v>85.66893424036306</v>
@@ -5069,13 +5069,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.3636562469824078</v>
+        <v>0.3570001039649029</v>
       </c>
       <c r="I14" s="4">
-        <v>0.300750080057929</v>
+        <v>0.2952199499887629</v>
       </c>
       <c r="J14" s="4">
-        <v>0.3460935919138404</v>
+        <v>0.3367954656263416</v>
       </c>
       <c r="K14" s="4">
         <v>62.87576935536109</v>
@@ -5119,13 +5119,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2618372053042038</v>
+        <v>0.2363477517596504</v>
       </c>
       <c r="I15" s="4">
-        <v>0.241336605757645</v>
+        <v>0.2199388308377165</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2017764067108546</v>
+        <v>0.1851795440547014</v>
       </c>
       <c r="K15" s="4">
         <v>94.81413994169158</v>
@@ -5169,13 +5169,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.3406056101502197</v>
+        <v>0.3491919136442922</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2783504243482554</v>
+        <v>0.2677054875535194</v>
       </c>
       <c r="J16" s="4">
-        <v>0.4138648101898807</v>
+        <v>0.3691272641687722</v>
       </c>
       <c r="K16" s="4">
         <v>54.84815354713315</v>
@@ -5219,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2865849828459746</v>
+        <v>0.2675900217689777</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2782931484814135</v>
+        <v>0.2647934641616047</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2116079862840902</v>
+        <v>0.1965200332737111</v>
       </c>
       <c r="K17" s="4">
         <v>93.0405733722059</v>
@@ -6922,16 +6922,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2810027420354251</v>
+        <v>0.2040162061645532</v>
       </c>
       <c r="O3" s="5">
         <v>34</v>
       </c>
       <c r="P3" s="4">
-        <v>0.268668297358239</v>
+        <v>0.2620742185731331</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2794979148540224</v>
+        <v>0.2679873293244471</v>
       </c>
       <c r="R3" s="5">
         <v>34</v>
@@ -6981,16 +6981,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.0002015337094225261</v>
+        <v>-0.05563699071653616</v>
       </c>
       <c r="O4" s="5">
         <v>34</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2496031851600816</v>
+        <v>0.2452217422981791</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2454400811621448</v>
+        <v>0.2408009063671891</v>
       </c>
       <c r="R4" s="5">
         <v>34</v>
@@ -7040,16 +7040,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6050201253568398</v>
+        <v>0.4638045501745438</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6244050799262166</v>
+        <v>0.548673008046876</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4706341499696249</v>
+        <v>0.4279088526237018</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -7222,16 +7222,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4826177789933662</v>
+        <v>0.414135875894786</v>
       </c>
       <c r="O3" s="5">
         <v>28</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3147195220832755</v>
+        <v>0.2995762971968582</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.240077318255421</v>
+        <v>0.2254990221942117</v>
       </c>
       <c r="R3" s="5">
         <v>28</v>
@@ -7281,16 +7281,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1067549110981166</v>
+        <v>0.075409584023447</v>
       </c>
       <c r="O4" s="5">
         <v>35</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2502892834782357</v>
+        <v>0.2477360630697653</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2438746272060862</v>
+        <v>0.2403528768695261</v>
       </c>
       <c r="R4" s="5">
         <v>35</v>
@@ -7338,16 +7338,16 @@
         <v>5</v>
       </c>
       <c r="N5" s="4">
-        <v>2.991832589187487</v>
+        <v>2.868873518749979</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5433664689372609</v>
+        <v>0.5228732905310096</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4271838086031335</v>
+        <v>0.4025919945156318</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -7520,16 +7520,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2510752142200603</v>
+        <v>0.164750483527996</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2297829220943131</v>
+        <v>0.209895082706572</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2297829220943131</v>
+        <v>0.209895082706572</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -7579,16 +7579,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1164593481131192</v>
+        <v>0.03419006015082005</v>
       </c>
       <c r="O4" s="5">
         <v>35</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2538637527843654</v>
+        <v>0.2429317916488627</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2478930289023583</v>
+        <v>0.2389992771047641</v>
       </c>
       <c r="R4" s="5">
         <v>35</v>
@@ -7638,16 +7638,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1100279383098811</v>
+        <v>-0.04558156724283435</v>
       </c>
       <c r="O5" s="5">
         <v>11</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4338122875471546</v>
+        <v>0.3831317036063145</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4067932217308141</v>
+        <v>0.3656516306637808</v>
       </c>
       <c r="R5" s="5">
         <v>11</v>
@@ -7820,16 +7820,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2274954013693949</v>
+        <v>0.1316210982287771</v>
       </c>
       <c r="O3" s="5">
         <v>35</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2597948596820749</v>
+        <v>0.2453568319021263</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2567604570696426</v>
+        <v>0.2391706484062492</v>
       </c>
       <c r="R3" s="5">
         <v>35</v>
@@ -7879,16 +7879,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01703144076074728</v>
+        <v>-0.06088542835018984</v>
       </c>
       <c r="O4" s="5">
         <v>31</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2375543408609851</v>
+        <v>0.2312630856705727</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2368253296582329</v>
+        <v>0.2281047111277719</v>
       </c>
       <c r="R4" s="5">
         <v>31</v>
@@ -7938,16 +7938,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3040431641461083</v>
+        <v>0.189229078296492</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.516006505970059</v>
+        <v>0.4799999772786497</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4319520743188541</v>
+        <v>0.4066458027441442</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -8120,16 +8120,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1014466699937715</v>
+        <v>0.02864559919190413</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2492023595185306</v>
+        <v>0.2350583256434449</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2492023595185306</v>
+        <v>0.2350583256434449</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -8179,16 +8179,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04114606045504258</v>
+        <v>-0.02165049935425145</v>
       </c>
       <c r="O4" s="5">
         <v>34</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2430071492417269</v>
+        <v>0.230573273687067</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2259487166761718</v>
+        <v>0.2164773519600198</v>
       </c>
       <c r="R4" s="5">
         <v>34</v>
@@ -8238,16 +8238,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2872938801501377</v>
+        <v>0.06083798229857962</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5721432568587291</v>
+        <v>0.4594395066373759</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4524347197460994</v>
+        <v>0.3966070433398485</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
